--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2024_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2024_arica_y_parinacota.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:48</t>
+    <t xml:space="preserve">2026-10-05 02:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -704,7 +704,7 @@
         <v>251451.25</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>307926.12</v>
+        <v>307926.13</v>
       </c>
     </row>
     <row r="3">
@@ -712,7 +712,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>244897.62</v>
+        <v>244897.63</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>303656.34</v>
@@ -847,7 +847,7 @@
         <v>260797.44</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>324105.12</v>
+        <v>324105.13</v>
       </c>
     </row>
     <row r="16">
@@ -913,7 +913,7 @@
         <v>275515.19</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>329863.62</v>
+        <v>329863.63</v>
       </c>
     </row>
     <row r="22">
@@ -965,7 +965,7 @@
         <v>27</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>280396.12</v>
+        <v>280396.13</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>340202.06</v>
@@ -1053,7 +1053,7 @@
         <v>35</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>276787.12</v>
+        <v>276787.13</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>323865.91</v>
@@ -1130,7 +1130,7 @@
         <v>42</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>281008.12</v>
+        <v>281008.13</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>338820.44</v>
@@ -1141,7 +1141,7 @@
         <v>43</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>280288.62</v>
+        <v>280288.63</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>335150.84</v>
@@ -1287,7 +1287,7 @@
         <v>327067.66</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>391178.62</v>
+        <v>391178.63</v>
       </c>
     </row>
     <row r="56">
@@ -1460,7 +1460,7 @@
         <v>72</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>368546.62</v>
+        <v>368546.63</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>436987.88</v>
@@ -1529,7 +1529,7 @@
         <v>372355.59</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>440497.12</v>
+        <v>440497.13</v>
       </c>
     </row>
     <row r="78">
@@ -1595,7 +1595,7 @@
         <v>381993.88</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>451935.62</v>
+        <v>451935.63</v>
       </c>
     </row>
     <row r="84">
